--- a/Packages/cn.etetet.numeric/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.numeric/Luban/Config/Base/__tables__.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -119,14 +119,14 @@
     <t>NumericType</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+    <t>Packages/cn.etetet.numeric/Luban/Config/Datas/NumericType.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -176,21 +176,21 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,7 +481,7 @@
     <col min="12" max="12" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1">
+    <row r="2" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -548,7 +548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1">
+    <row r="3" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -571,83 +571,89 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="str">
-        <f t="shared" ref="C4" si="0">_xlfn.CONCAT("ET.",B4,"ConfigCategory")</f>
+      <c r="C4" s="0" t="str">
+        <f>_xlfn.CONCAT("ET.",B4,"ConfigCategory")</f>
         <v>ET.NumericTypeConfigCategory</v>
       </c>
-      <c r="D4" t="str">
-        <f t="shared" ref="D4" si="1">_xlfn.CONCAT(B4,"Config")</f>
+      <c r="D4" s="0" t="str">
+        <f>_xlfn.CONCAT(B4,"Config")</f>
         <v>NumericTypeConfig</v>
       </c>
-      <c r="E4" t="b">
+      <c r="E4" s="0" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L4" t="str">
-        <f t="shared" ref="L4" si="2">_xlfn.CONCAT(B4,"ConfigCategory")</f>
+      <c r="L4" s="0" t="str">
+        <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
         <v>NumericTypeConfigCategory</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5">
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9">
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10">
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11">
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13">
       <c r="B13" s="2"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15">
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16">
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17">
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18">
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19">
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20">
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21">
       <c r="B21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>